--- a/Design/Configs/Treasure.xlsx
+++ b/Design/Configs/Treasure.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE7B16F-5E59-407C-B430-4EDECF9425B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84A03EA-E1B3-4454-A1CA-5DD5F6AE2787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="4740" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="1140" windowWidth="25755" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,10 +86,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>血包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EffectParams</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,6 +107,18 @@
   </si>
   <si>
     <t>[[0]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血包1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血包2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血包3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -466,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.625" customWidth="1"/>
@@ -492,7 +500,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>5</v>
@@ -501,10 +509,10 @@
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -512,10 +520,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1">
         <v>14</v>
@@ -533,10 +541,74 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Configs/Treasure.xlsx
+++ b/Design/Configs/Treasure.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84A03EA-E1B3-4454-A1CA-5DD5F6AE2787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822E2F08-4321-4900-9B44-E8D2C8A1EEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1140" windowWidth="25755" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="-90" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -558,7 +558,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -590,7 +590,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="1">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>

--- a/Design/Configs/Treasure.xlsx
+++ b/Design/Configs/Treasure.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822E2F08-4321-4900-9B44-E8D2C8A1EEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0CAA5F-D15C-4839-B006-C1A1C2C76D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="-90" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26700" yWindow="-30" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,10 +90,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>加20血的宝物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EffectIds</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -102,14 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[[0]]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>血包1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -119,6 +107,34 @@
   </si>
   <si>
     <t>血包3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[10001]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加400血的宝物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加800血的宝物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[400]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[800]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加2000血的宝物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[2000]]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -500,7 +516,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>5</v>
@@ -509,7 +525,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>7</v>
@@ -520,10 +536,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1">
         <v>14</v>
@@ -541,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -552,10 +568,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1">
         <v>15</v>
@@ -573,10 +589,10 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -584,10 +600,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1">
         <v>16</v>
@@ -605,10 +621,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
